--- a/outputs/submission_tables_xlsx/Supplementary Table 4.xlsx
+++ b/outputs/submission_tables_xlsx/Supplementary Table 4.xlsx
@@ -7,8 +7,7 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="A - Sex-specific 2050" sheetId="1" r:id="rId1"/>
-    <sheet name="B - Reconciliation" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -344,13 +343,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:I55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Sex</t>
+          <t>Model</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -360,159 +359,1820 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Estimand</t>
+          <t>Group</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>DALYs</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>DALYs scenario range, low</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>DALYs scenario range, high</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>VLW (billion constant-2023 USD)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>VLW scenario range, low (billion constant-2023 USD)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>VLW scenario range, high (billion constant-2023 USD)</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Ljung-Box p value</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Residual autocorrelation detected at the 5% level</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B2">
-        <v>2050</v>
+        <v>2024</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Direct sex-specific VLW ARIMA forecast (secondary; descriptive only, not an inferential comparison)</t>
+          <t>All LMICs</t>
         </is>
       </c>
       <c r="D2">
-        <v>676.5479562410777</v>
+        <v>6385930.481173182</v>
       </c>
       <c r="E2">
-        <v>603.8925438579722</v>
+        <v>6256703.557875448</v>
       </c>
       <c r="F2">
-        <v>749.2033686241832</v>
+        <v>6513073.441826616</v>
       </c>
       <c r="G2">
-        <v>0.2364105266986328</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
+        <v>753.1262011084686</v>
+      </c>
+      <c r="H2">
+        <v>737.4864135230475</v>
+      </c>
+      <c r="I2">
+        <v>768.4637947684041</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Female</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B3">
-        <v>2050</v>
+        <v>2025</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Direct sex-specific VLW ARIMA forecast (secondary; descriptive only, not an inferential comparison)</t>
+          <t>All LMICs</t>
         </is>
       </c>
       <c r="D3">
-        <v>546.3081902695898</v>
+        <v>6484053.143240076</v>
       </c>
       <c r="E3">
-        <v>407.0696547093709</v>
+        <v>6229768.678892773</v>
       </c>
       <c r="F3">
-        <v>685.5467258298086</v>
+        <v>6739741.483809171</v>
       </c>
       <c r="G3">
-        <v>0.3948102268526551</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Quantity</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Value (billion constant-2023 USD, except relative difference)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Primary: DALY-derived VLW, all LMICs (ARIMA)</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>1195.059287771596</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Secondary: direct sex-specific VLW ARIMA, Male + Female</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>1222.856146510668</v>
+        <v>759.6484931687615</v>
+      </c>
+      <c r="H3">
+        <v>728.0107627369093</v>
+      </c>
+      <c r="I3">
+        <v>791.2013331644466</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Absolute difference</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B4">
-        <v>27.79685873907101</v>
+        <v>2026</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D4">
+        <v>6818412.753237404</v>
+      </c>
+      <c r="E4">
+        <v>6486684.596101928</v>
+      </c>
+      <c r="F4">
+        <v>7151017.879202027</v>
+      </c>
+      <c r="G4">
+        <v>799.3056257577343</v>
+      </c>
+      <c r="H4">
+        <v>758.8036317242273</v>
+      </c>
+      <c r="I4">
+        <v>839.8809564305525</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Relative difference (%)</t>
+          <t>ARIMA</t>
         </is>
       </c>
       <c r="B5">
-        <v>2.325981566228673</v>
+        <v>2027</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>7145534.597800401</v>
+      </c>
+      <c r="E5">
+        <v>6782221.132124072</v>
+      </c>
+      <c r="F5">
+        <v>7512820.541764076</v>
+      </c>
+      <c r="G5">
+        <v>837.9475818235107</v>
+      </c>
+      <c r="H5">
+        <v>794.9938562086805</v>
+      </c>
+      <c r="I5">
+        <v>881.2135971901121</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B6">
+        <v>2028</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>7273026.55102649</v>
+      </c>
+      <c r="E6">
+        <v>6870876.071594755</v>
+      </c>
+      <c r="F6">
+        <v>7672048.94587773</v>
+      </c>
+      <c r="G6">
+        <v>848.5892412711898</v>
+      </c>
+      <c r="H6">
+        <v>803.1744100930001</v>
+      </c>
+      <c r="I6">
+        <v>893.532500174393</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B7">
+        <v>2029</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>7286494.066497587</v>
+      </c>
+      <c r="E7">
+        <v>6839017.080101709</v>
+      </c>
+      <c r="F7">
+        <v>7733018.368934015</v>
+      </c>
+      <c r="G7">
+        <v>843.2377142402802</v>
+      </c>
+      <c r="H7">
+        <v>794.0113694502335</v>
+      </c>
+      <c r="I7">
+        <v>892.1650577323776</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>2030</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D8">
+        <v>7396484.405171482</v>
+      </c>
+      <c r="E8">
+        <v>6882639.879354036</v>
+      </c>
+      <c r="F8">
+        <v>7910892.97902303</v>
+      </c>
+      <c r="G8">
+        <v>851.4245789902552</v>
+      </c>
+      <c r="H8">
+        <v>795.722359303473</v>
+      </c>
+      <c r="I8">
+        <v>907.2194949305048</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B9">
+        <v>2031</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>7658797.02631495</v>
+      </c>
+      <c r="E9">
+        <v>7076255.737006145</v>
+      </c>
+      <c r="F9">
+        <v>8239863.738054734</v>
+      </c>
+      <c r="G9">
+        <v>880.9763258334419</v>
+      </c>
+      <c r="H9">
+        <v>818.5266408831156</v>
+      </c>
+      <c r="I9">
+        <v>943.2138483700116</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B10">
+        <v>2032</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D10">
+        <v>7932877.485047355</v>
+      </c>
+      <c r="E10">
+        <v>7310519.484959359</v>
+      </c>
+      <c r="F10">
+        <v>8560792.653810833</v>
+      </c>
+      <c r="G10">
+        <v>912.1786418415828</v>
+      </c>
+      <c r="H10">
+        <v>847.2711250582422</v>
+      </c>
+      <c r="I10">
+        <v>977.6108227803744</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B11">
+        <v>2033</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>8088077.180221331</v>
+      </c>
+      <c r="E11">
+        <v>7415726.900320183</v>
+      </c>
+      <c r="F11">
+        <v>8753620.37696901</v>
+      </c>
+      <c r="G11">
+        <v>926.7066180525624</v>
+      </c>
+      <c r="H11">
+        <v>858.8863064431592</v>
+      </c>
+      <c r="I11">
+        <v>994.0383406406784</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B12">
+        <v>2034</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D12">
+        <v>8162069.659676233</v>
+      </c>
+      <c r="E12">
+        <v>7451352.638938699</v>
+      </c>
+      <c r="F12">
+        <v>8886837.656547518</v>
+      </c>
+      <c r="G12">
+        <v>929.8443855506274</v>
+      </c>
+      <c r="H12">
+        <v>859.2157548058652</v>
+      </c>
+      <c r="I12">
+        <v>1001.698721914306</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B13">
+        <v>2035</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D13">
+        <v>8285539.982833493</v>
+      </c>
+      <c r="E13">
+        <v>7503121.206709398</v>
+      </c>
+      <c r="F13">
+        <v>9062825.398312028</v>
+      </c>
+      <c r="G13">
+        <v>939.9219669734108</v>
+      </c>
+      <c r="H13">
+        <v>863.3420645114244</v>
+      </c>
+      <c r="I13">
+        <v>1016.125181826662</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B14">
+        <v>2036</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D14">
+        <v>8505909.274544235</v>
+      </c>
+      <c r="E14">
+        <v>7647477.319879425</v>
+      </c>
+      <c r="F14">
+        <v>9359705.428337911</v>
+      </c>
+      <c r="G14">
+        <v>963.5906987159937</v>
+      </c>
+      <c r="H14">
+        <v>880.935063291965</v>
+      </c>
+      <c r="I14">
+        <v>1045.92975087378</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B15">
+        <v>2037</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D15">
+        <v>8743624.971687481</v>
+      </c>
+      <c r="E15">
+        <v>7841417.857998501</v>
+      </c>
+      <c r="F15">
+        <v>9639485.009881159</v>
+      </c>
+      <c r="G15">
+        <v>989.69245536339</v>
+      </c>
+      <c r="H15">
+        <v>904.133546364483</v>
+      </c>
+      <c r="I15">
+        <v>1074.243225127089</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B16">
+        <v>2038</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D16">
+        <v>8911643.776201496</v>
+      </c>
+      <c r="E16">
+        <v>7950687.984453021</v>
+      </c>
+      <c r="F16">
+        <v>9861094.489036122</v>
+      </c>
+      <c r="G16">
+        <v>1006.018453210795</v>
+      </c>
+      <c r="H16">
+        <v>916.7294846902752</v>
+      </c>
+      <c r="I16">
+        <v>1093.985807338034</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B17">
+        <v>2039</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D17">
+        <v>9023413.903441371</v>
+      </c>
+      <c r="E17">
+        <v>8006774.564465372</v>
+      </c>
+      <c r="F17">
+        <v>10050503.54820297</v>
+      </c>
+      <c r="G17">
+        <v>1014.454952959974</v>
+      </c>
+      <c r="H17">
+        <v>921.4897286729718</v>
+      </c>
+      <c r="I17">
+        <v>1108.159378031869</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B18">
+        <v>2040</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D18">
+        <v>9158997.614921698</v>
+      </c>
+      <c r="E18">
+        <v>8067787.853038183</v>
+      </c>
+      <c r="F18">
+        <v>10248644.60090174</v>
+      </c>
+      <c r="G18">
+        <v>1026.231570853821</v>
+      </c>
+      <c r="H18">
+        <v>927.946720097664</v>
+      </c>
+      <c r="I18">
+        <v>1124.587783907198</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B19">
+        <v>2041</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D19">
+        <v>9355411.454337455</v>
+      </c>
+      <c r="E19">
+        <v>8217538.547246261</v>
+      </c>
+      <c r="F19">
+        <v>10505638.22094635</v>
+      </c>
+      <c r="G19">
+        <v>1046.540285890548</v>
+      </c>
+      <c r="H19">
+        <v>945.1149262674676</v>
+      </c>
+      <c r="I19">
+        <v>1148.964589017669</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B20">
+        <v>2042</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D20">
+        <v>9568707.450410992</v>
+      </c>
+      <c r="E20">
+        <v>8359553.72558366</v>
+      </c>
+      <c r="F20">
+        <v>10780696.23200524</v>
+      </c>
+      <c r="G20">
+        <v>1069.216909815094</v>
+      </c>
+      <c r="H20">
+        <v>962.8918098161962</v>
+      </c>
+      <c r="I20">
+        <v>1176.517076838941</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B21">
+        <v>2043</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D21">
+        <v>9741852.958625756</v>
+      </c>
+      <c r="E21">
+        <v>8471308.458223071</v>
+      </c>
+      <c r="F21">
+        <v>11012606.38545239</v>
+      </c>
+      <c r="G21">
+        <v>1086.261984466742</v>
+      </c>
+      <c r="H21">
+        <v>975.3524179182706</v>
+      </c>
+      <c r="I21">
+        <v>1197.375335710911</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B22">
+        <v>2044</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D22">
+        <v>9876898.27660783</v>
+      </c>
+      <c r="E22">
+        <v>8536038.632106667</v>
+      </c>
+      <c r="F22">
+        <v>11218076.72703231</v>
+      </c>
+      <c r="G22">
+        <v>1097.963086727399</v>
+      </c>
+      <c r="H22">
+        <v>983.1702676901144</v>
+      </c>
+      <c r="I22">
+        <v>1213.292849052719</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B23">
+        <v>2045</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D23">
+        <v>10022236.75492662</v>
+      </c>
+      <c r="E23">
+        <v>8613824.906902231</v>
+      </c>
+      <c r="F23">
+        <v>11429213.33395139</v>
+      </c>
+      <c r="G23">
+        <v>1111.107918384667</v>
+      </c>
+      <c r="H23">
+        <v>991.466172193337</v>
+      </c>
+      <c r="I23">
+        <v>1230.716620629998</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B24">
+        <v>2046</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D24">
+        <v>10205269.19988474</v>
+      </c>
+      <c r="E24">
+        <v>8738546.049833704</v>
+      </c>
+      <c r="F24">
+        <v>11673265.15356857</v>
+      </c>
+      <c r="G24">
+        <v>1129.539745088347</v>
+      </c>
+      <c r="H24">
+        <v>1006.678268296667</v>
+      </c>
+      <c r="I24">
+        <v>1252.575011173897</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B25">
+        <v>2047</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D25">
+        <v>10402453.44075263</v>
+      </c>
+      <c r="E25">
+        <v>8849271.664503474</v>
+      </c>
+      <c r="F25">
+        <v>11959275.1359653</v>
+      </c>
+      <c r="G25">
+        <v>1149.956517435682</v>
+      </c>
+      <c r="H25">
+        <v>1021.554660787609</v>
+      </c>
+      <c r="I25">
+        <v>1279.774145735835</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B26">
+        <v>2048</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D26">
+        <v>10576977.00562762</v>
+      </c>
+      <c r="E26">
+        <v>8956925.689504016</v>
+      </c>
+      <c r="F26">
+        <v>12178493.29783582</v>
+      </c>
+      <c r="G26">
+        <v>1167.194879750738</v>
+      </c>
+      <c r="H26">
+        <v>1033.707674243769</v>
+      </c>
+      <c r="I26">
+        <v>1299.321001586261</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B27">
+        <v>2049</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D27">
+        <v>10726173.77481474</v>
+      </c>
+      <c r="E27">
+        <v>9040484.710261021</v>
+      </c>
+      <c r="F27">
+        <v>12429384.81237107</v>
+      </c>
+      <c r="G27">
+        <v>1180.880879306403</v>
+      </c>
+      <c r="H27">
+        <v>1043.466856758762</v>
+      </c>
+      <c r="I27">
+        <v>1320.266835033303</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ARIMA</t>
+        </is>
+      </c>
+      <c r="B28">
+        <v>2050</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D28">
+        <v>10878881.20456531</v>
+      </c>
+      <c r="E28">
+        <v>9103277.081217671</v>
+      </c>
+      <c r="F28">
+        <v>12630985.45819847</v>
+      </c>
+      <c r="G28">
+        <v>1195.059287771596</v>
+      </c>
+      <c r="H28">
+        <v>1051.202088483295</v>
+      </c>
+      <c r="I28">
+        <v>1336.86092397161</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B29">
+        <v>2024</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D29">
+        <v>6668300.135051625</v>
+      </c>
+      <c r="E29">
+        <v>6489833.01982097</v>
+      </c>
+      <c r="F29">
+        <v>6850108.755812965</v>
+      </c>
+      <c r="G29">
+        <v>792.7249088614592</v>
+      </c>
+      <c r="H29">
+        <v>769.6250146242886</v>
+      </c>
+      <c r="I29">
+        <v>816.285423557164</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B30">
+        <v>2025</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D30">
+        <v>6864116.143930243</v>
+      </c>
+      <c r="E30">
+        <v>6585344.456203932</v>
+      </c>
+      <c r="F30">
+        <v>7139683.473648266</v>
+      </c>
+      <c r="G30">
+        <v>813.0737867585191</v>
+      </c>
+      <c r="H30">
+        <v>777.0740728031703</v>
+      </c>
+      <c r="I30">
+        <v>848.551736342708</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B31">
+        <v>2026</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D31">
+        <v>7056015.823324386</v>
+      </c>
+      <c r="E31">
+        <v>6686728.055977402</v>
+      </c>
+      <c r="F31">
+        <v>7426236.894702817</v>
+      </c>
+      <c r="G31">
+        <v>833.0156859308702</v>
+      </c>
+      <c r="H31">
+        <v>785.8738229163051</v>
+      </c>
+      <c r="I31">
+        <v>880.1798715229402</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B32">
+        <v>2027</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D32">
+        <v>7244077.500009881</v>
+      </c>
+      <c r="E32">
+        <v>6776068.649276694</v>
+      </c>
+      <c r="F32">
+        <v>7708907.334939033</v>
+      </c>
+      <c r="G32">
+        <v>852.5587459763425</v>
+      </c>
+      <c r="H32">
+        <v>793.6324165423663</v>
+      </c>
+      <c r="I32">
+        <v>911.1850733368708</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B33">
+        <v>2028</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D33">
+        <v>7428377.934223318</v>
+      </c>
+      <c r="E33">
+        <v>6866398.885259788</v>
+      </c>
+      <c r="F33">
+        <v>7987502.135558477</v>
+      </c>
+      <c r="G33">
+        <v>871.710943700342</v>
+      </c>
+      <c r="H33">
+        <v>801.692262875908</v>
+      </c>
+      <c r="I33">
+        <v>941.667161936508</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B34">
+        <v>2029</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D34">
+        <v>7608992.350992906</v>
+      </c>
+      <c r="E34">
+        <v>6945525.546176059</v>
+      </c>
+      <c r="F34">
+        <v>8267705.162509799</v>
+      </c>
+      <c r="G34">
+        <v>890.4800963717098</v>
+      </c>
+      <c r="H34">
+        <v>808.3364797787</v>
+      </c>
+      <c r="I34">
+        <v>972.1095453166638</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B35">
+        <v>2030</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D35">
+        <v>7785994.470842712</v>
+      </c>
+      <c r="E35">
+        <v>7014800.990844799</v>
+      </c>
+      <c r="F35">
+        <v>8548881.024780871</v>
+      </c>
+      <c r="G35">
+        <v>908.873864913461</v>
+      </c>
+      <c r="H35">
+        <v>814.3468136465086</v>
+      </c>
+      <c r="I35">
+        <v>1003.029415963643</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B36">
+        <v>2031</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D36">
+        <v>7959456.53988282</v>
+      </c>
+      <c r="E36">
+        <v>7085867.972309028</v>
+      </c>
+      <c r="F36">
+        <v>8834959.130078422</v>
+      </c>
+      <c r="G36">
+        <v>926.8997570297126</v>
+      </c>
+      <c r="H36">
+        <v>820.3628358071182</v>
+      </c>
+      <c r="I36">
+        <v>1033.948739164709</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B37">
+        <v>2032</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D37">
+        <v>8129449.359297682</v>
+      </c>
+      <c r="E37">
+        <v>7140008.103879496</v>
+      </c>
+      <c r="F37">
+        <v>9121801.131888898</v>
+      </c>
+      <c r="G37">
+        <v>944.5651302700676</v>
+      </c>
+      <c r="H37">
+        <v>823.8182164358851</v>
+      </c>
+      <c r="I37">
+        <v>1065.021595733013</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B38">
+        <v>2033</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D38">
+        <v>8296042.314244688</v>
+      </c>
+      <c r="E38">
+        <v>7198366.213646475</v>
+      </c>
+      <c r="F38">
+        <v>9391449.731407516</v>
+      </c>
+      <c r="G38">
+        <v>961.8771950327152</v>
+      </c>
+      <c r="H38">
+        <v>828.9812659238846</v>
+      </c>
+      <c r="I38">
+        <v>1093.532142915421</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B39">
+        <v>2034</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D39">
+        <v>8459303.402174789</v>
+      </c>
+      <c r="E39">
+        <v>7240080.720110877</v>
+      </c>
+      <c r="F39">
+        <v>9661731.062114349</v>
+      </c>
+      <c r="G39">
+        <v>978.8430175074679</v>
+      </c>
+      <c r="H39">
+        <v>832.3206988400149</v>
+      </c>
+      <c r="I39">
+        <v>1122.31831985919</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B40">
+        <v>2035</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D40">
+        <v>8619299.260586683</v>
+      </c>
+      <c r="E40">
+        <v>7301367.421013604</v>
+      </c>
+      <c r="F40">
+        <v>9949356.700296115</v>
+      </c>
+      <c r="G40">
+        <v>995.4695225599364</v>
+      </c>
+      <c r="H40">
+        <v>837.8278903133489</v>
+      </c>
+      <c r="I40">
+        <v>1154.807759323385</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B41">
+        <v>2036</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D41">
+        <v>8776095.194225926</v>
+      </c>
+      <c r="E41">
+        <v>7334149.055949235</v>
+      </c>
+      <c r="F41">
+        <v>10215075.2545766</v>
+      </c>
+      <c r="G41">
+        <v>1011.763496558022</v>
+      </c>
+      <c r="H41">
+        <v>839.9057502296904</v>
+      </c>
+      <c r="I41">
+        <v>1184.215018794574</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B42">
+        <v>2037</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D42">
+        <v>8929755.20174006</v>
+      </c>
+      <c r="E42">
+        <v>7351610.604085796</v>
+      </c>
+      <c r="F42">
+        <v>10505483.49774765</v>
+      </c>
+      <c r="G42">
+        <v>1027.73159014188</v>
+      </c>
+      <c r="H42">
+        <v>841.8517262330114</v>
+      </c>
+      <c r="I42">
+        <v>1214.256530297438</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B43">
+        <v>2038</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D43">
+        <v>9080342.001800634</v>
+      </c>
+      <c r="E43">
+        <v>7393393.253672212</v>
+      </c>
+      <c r="F43">
+        <v>10764723.23987956</v>
+      </c>
+      <c r="G43">
+        <v>1043.380320938479</v>
+      </c>
+      <c r="H43">
+        <v>842.7001457665018</v>
+      </c>
+      <c r="I43">
+        <v>1242.894822680191</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B44">
+        <v>2039</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D44">
+        <v>9227917.058702787</v>
+      </c>
+      <c r="E44">
+        <v>7410694.860755126</v>
+      </c>
+      <c r="F44">
+        <v>11022764.16149154</v>
+      </c>
+      <c r="G44">
+        <v>1058.716076221877</v>
+      </c>
+      <c r="H44">
+        <v>843.9965165530288</v>
+      </c>
+      <c r="I44">
+        <v>1271.29267117578</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B45">
+        <v>2040</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D45">
+        <v>9372540.60745283</v>
+      </c>
+      <c r="E45">
+        <v>7446562.754567048</v>
+      </c>
+      <c r="F45">
+        <v>11302504.80284047</v>
+      </c>
+      <c r="G45">
+        <v>1073.745115520283</v>
+      </c>
+      <c r="H45">
+        <v>846.7685682806504</v>
+      </c>
+      <c r="I45">
+        <v>1302.23496990663</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B46">
+        <v>2041</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D46">
+        <v>9514271.678354086</v>
+      </c>
+      <c r="E46">
+        <v>7435878.785618326</v>
+      </c>
+      <c r="F46">
+        <v>11580352.18471957</v>
+      </c>
+      <c r="G46">
+        <v>1088.473573170983</v>
+      </c>
+      <c r="H46">
+        <v>845.2599019644178</v>
+      </c>
+      <c r="I46">
+        <v>1331.111846404671</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B47">
+        <v>2042</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D47">
+        <v>9653168.121101009</v>
+      </c>
+      <c r="E47">
+        <v>7465390.86425277</v>
+      </c>
+      <c r="F47">
+        <v>11852904.78721754</v>
+      </c>
+      <c r="G47">
+        <v>1102.907460824167</v>
+      </c>
+      <c r="H47">
+        <v>846.7458922258048</v>
+      </c>
+      <c r="I47">
+        <v>1359.709558523411</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B48">
+        <v>2043</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D48">
+        <v>9789286.628391411</v>
+      </c>
+      <c r="E48">
+        <v>7465076.759479545</v>
+      </c>
+      <c r="F48">
+        <v>12121458.19397255</v>
+      </c>
+      <c r="G48">
+        <v>1117.052669896674</v>
+      </c>
+      <c r="H48">
+        <v>844.7734136322182</v>
+      </c>
+      <c r="I48">
+        <v>1389.531160550536</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B49">
+        <v>2044</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D49">
+        <v>9922682.759066457</v>
+      </c>
+      <c r="E49">
+        <v>7463625.920113379</v>
+      </c>
+      <c r="F49">
+        <v>12394665.38820609</v>
+      </c>
+      <c r="G49">
+        <v>1130.914973976671</v>
+      </c>
+      <c r="H49">
+        <v>845.1289686868502</v>
+      </c>
+      <c r="I49">
+        <v>1418.852249272346</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B50">
+        <v>2045</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D50">
+        <v>10053410.96078784</v>
+      </c>
+      <c r="E50">
+        <v>7455791.380866018</v>
+      </c>
+      <c r="F50">
+        <v>12638858.49307961</v>
+      </c>
+      <c r="G50">
+        <v>1144.50003118023</v>
+      </c>
+      <c r="H50">
+        <v>844.141654955273</v>
+      </c>
+      <c r="I50">
+        <v>1446.947381927933</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B51">
+        <v>2046</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D51">
+        <v>10181524.59226144</v>
+      </c>
+      <c r="E51">
+        <v>7450354.781960918</v>
+      </c>
+      <c r="F51">
+        <v>12916172.35589679</v>
+      </c>
+      <c r="G51">
+        <v>1157.813386460774</v>
+      </c>
+      <c r="H51">
+        <v>840.0758914979032</v>
+      </c>
+      <c r="I51">
+        <v>1476.391433159321</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>2047</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D52">
+        <v>10307075.94501649</v>
+      </c>
+      <c r="E52">
+        <v>7452616.194210742</v>
+      </c>
+      <c r="F52">
+        <v>13149532.74352802</v>
+      </c>
+      <c r="G52">
+        <v>1170.860473872345</v>
+      </c>
+      <c r="H52">
+        <v>838.4745375859903</v>
+      </c>
+      <c r="I52">
+        <v>1499.596352231671</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>2048</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D53">
+        <v>10430116.26474912</v>
+      </c>
+      <c r="E53">
+        <v>7463955.205584987</v>
+      </c>
+      <c r="F53">
+        <v>13438447.74488524</v>
+      </c>
+      <c r="G53">
+        <v>1183.646618787588</v>
+      </c>
+      <c r="H53">
+        <v>841.4196550170902</v>
+      </c>
+      <c r="I53">
+        <v>1532.417548668054</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B54">
+        <v>2049</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D54">
+        <v>10550695.77223915</v>
+      </c>
+      <c r="E54">
+        <v>7417997.595063822</v>
+      </c>
+      <c r="F54">
+        <v>13662934.79487643</v>
+      </c>
+      <c r="G54">
+        <v>1196.177040071393</v>
+      </c>
+      <c r="H54">
+        <v>833.8115370121938</v>
+      </c>
+      <c r="I54">
+        <v>1556.089970370012</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ETS</t>
+        </is>
+      </c>
+      <c r="B55">
+        <v>2050</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>All LMICs</t>
+        </is>
+      </c>
+      <c r="D55">
+        <v>10668863.68384837</v>
+      </c>
+      <c r="E55">
+        <v>7395645.411140123</v>
+      </c>
+      <c r="F55">
+        <v>13932763.26519256</v>
+      </c>
+      <c r="G55">
+        <v>1208.45685221105</v>
+      </c>
+      <c r="H55">
+        <v>830.7994720229001</v>
+      </c>
+      <c r="I55">
+        <v>1586.555391080247</v>
       </c>
     </row>
   </sheetData>
